--- a/artfynd/A 44009-2025 artfynd.xlsx
+++ b/artfynd/A 44009-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137395438</v>
       </c>
       <c r="B2" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137395464</v>
       </c>
       <c r="B3" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137395429</v>
       </c>
       <c r="B4" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>137395443</v>
       </c>
       <c r="B5" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>137395451</v>
       </c>
       <c r="B6" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>137395460</v>
       </c>
       <c r="B7" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>137395408</v>
       </c>
       <c r="B9" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>137395419</v>
       </c>
       <c r="B10" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 44009-2025 artfynd.xlsx
+++ b/artfynd/A 44009-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137395438</v>
       </c>
       <c r="B2" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137395464</v>
       </c>
       <c r="B3" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137395429</v>
       </c>
       <c r="B4" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>137395443</v>
       </c>
       <c r="B5" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>137395451</v>
       </c>
       <c r="B6" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>137395460</v>
       </c>
       <c r="B7" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>137395408</v>
       </c>
       <c r="B9" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>137395419</v>
       </c>
       <c r="B10" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 44009-2025 artfynd.xlsx
+++ b/artfynd/A 44009-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137395438</v>
       </c>
       <c r="B2" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137395464</v>
       </c>
       <c r="B3" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137395429</v>
       </c>
       <c r="B4" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>137395443</v>
       </c>
       <c r="B5" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>137395451</v>
       </c>
       <c r="B6" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>137395460</v>
       </c>
       <c r="B7" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>137395408</v>
       </c>
       <c r="B9" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>137395419</v>
       </c>
       <c r="B10" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 44009-2025 artfynd.xlsx
+++ b/artfynd/A 44009-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137395438</v>
       </c>
       <c r="B2" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137395464</v>
       </c>
       <c r="B3" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137395429</v>
       </c>
       <c r="B4" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>137395443</v>
       </c>
       <c r="B5" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>137395451</v>
       </c>
       <c r="B6" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>137395460</v>
       </c>
       <c r="B7" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>137395432</v>
       </c>
       <c r="B8" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>137395408</v>
       </c>
       <c r="B9" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>137395419</v>
       </c>
       <c r="B10" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
